--- a/public/docs/Tipo do extrato.xlsx
+++ b/public/docs/Tipo do extrato.xlsx
@@ -30,7 +30,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <r>
-      <t xml:space="preserve">Saldo {NOME} R$ </t>
+      <t xml:space="preserve">                                                                Saldo {NOME} R$ </t>
     </r>
     <r>
       <rPr>
@@ -58,6 +58,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
       <t xml:space="preserve">U$ </t>
     </r>
     <r>
@@ -84,7 +91,7 @@
     </r>
   </si>
   <si>
-    <t>Entrada R$</t>
+    <t>Entrada Raa$</t>
   </si>
   <si>
     <t>Saída U$</t>
@@ -329,7 +336,7 @@
       <b/>
       <u/>
       <sz val="10"/>
-      <color rgb="FF1155CC"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="major"/>
@@ -338,7 +345,7 @@
       <b/>
       <u/>
       <sz val="10"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF1155CC"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="major"/>
@@ -884,7 +891,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -894,8 +901,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -903,12 +915,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1400,7 +1416,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1411,17 +1427,17 @@
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="4"/>
-      <c r="H2" s="10"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="4"/>
-      <c r="K2" s="10"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" customHeight="1" spans="1:11">
       <c r="A3" s="5" t="s">
@@ -1436,7 +1452,7 @@
       <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -1445,7 +1461,7 @@
       <c r="G3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="5" t="s">
@@ -1454,100 +1470,100 @@
       <c r="J3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="5">
+      <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="K4" s="13"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="15"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
+      <c r="K4" s="14"/>
     </row>
     <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="5">
+      <c r="A5" s="7">
         <v>2</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-      <c r="K5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="15"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" customHeight="1" spans="1:11">
-      <c r="A6" s="5">
+      <c r="A6" s="7">
         <v>3</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="K6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="15"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-      <c r="K7" s="13"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="15"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="5">
+      <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-      <c r="K8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="5">
+      <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-      <c r="K9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+      <c r="K9" s="14"/>
     </row>
     <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-      <c r="K10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" customHeight="1" spans="1:11">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="15" t="s">
+      <c r="D11" s="9"/>
+      <c r="E11" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="9" t="s">
+      <c r="F11" s="8"/>
+      <c r="G11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="9" t="s">
+      <c r="H11" s="17"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="16"/>
+      <c r="K11" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1557,7 +1573,7 @@
     <mergeCell ref="I2:K2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="Saldo {NOME} R$ X.XXX,XX"/>
+    <hyperlink ref="A1" r:id="rId1" display="                                                                Saldo {NOME} R$ X.XXX,XX"/>
     <hyperlink ref="K1" r:id="rId1" display="U$ X.XXX,00"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
